--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.58367325968126</v>
+        <v>5.782346904698204</v>
       </c>
       <c r="D2" t="n">
-        <v>35.35212193682911</v>
+        <v>5.744719814734731</v>
       </c>
       <c r="E2" t="n">
-        <v>10.88392380608567</v>
+        <v>1.768637618488921</v>
       </c>
       <c r="F2" t="n">
-        <v>10.96938199294128</v>
+        <v>1.782524573852958</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.50037570046711</v>
+        <v>5.931311051325905</v>
       </c>
       <c r="D3" t="n">
-        <v>36.76989574658332</v>
+        <v>5.97510805881979</v>
       </c>
       <c r="E3" t="n">
-        <v>10.88392380608567</v>
+        <v>1.768637618488921</v>
       </c>
       <c r="F3" t="n">
-        <v>10.96938199294128</v>
+        <v>1.782524573852958</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.96738838648984</v>
+        <v>2.107200612804599</v>
       </c>
       <c r="D4" t="n">
-        <v>12.82385165864979</v>
+        <v>2.083875894530591</v>
       </c>
       <c r="E4" t="n">
-        <v>10.88392380608567</v>
+        <v>1.768637618488921</v>
       </c>
       <c r="F4" t="n">
-        <v>10.96938199294128</v>
+        <v>1.782524573852958</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
